--- a/public/templates/catalog-import-04.xlsx
+++ b/public/templates/catalog-import-04.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R8d3634489ad54af6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_兼容压接" sheetId="2" r:id="R9c2b9ddf295f4ff5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R21446dd9afad4da0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R594f3e8b0b67492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R857c09c25b5743ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_兼容压接" sheetId="2" r:id="R9fa5c98fba924826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R433040ece78e4223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R3a5b30a1564e4c0d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,7 +78,13 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>

--- a/public/templates/catalog-import-04.xlsx
+++ b/public/templates/catalog-import-04.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="R857c09c25b5743ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_兼容压接" sheetId="2" r:id="R9fa5c98fba924826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R433040ece78e4223"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="R3a5b30a1564e4c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_填写说明" sheetId="1" r:id="Rb77c6e2ea1e24e58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_兼容压接" sheetId="2" r:id="R399fad748edb4d2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_字段字典" sheetId="3" r:id="R9b90953cd9d2467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_下拉选项" sheetId="4" r:id="Re1467e0871584790"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -542,8 +542,8 @@
       <x:c r="E1" s="11" t="str">
         <x:v>Hose End SKU / 接头SKU [必填]</x:v>
       </x:c>
-      <x:c r="F1" s="11" t="str">
-        <x:v>Ferrule SKU / 套筒SKU [必填]</x:v>
+      <x:c r="F1" s="14" t="str">
+        <x:v>Ferrule SKU / 套筒SKU [选填]</x:v>
       </x:c>
       <x:c r="G1" s="14" t="str">
         <x:v>Assembly Method / 装配方法 [选填]</x:v>
@@ -621,7 +621,7 @@
       <x:c r="C2" s="13"/>
       <x:c r="D2" s="13"/>
       <x:c r="E2" s="13"/>
-      <x:c r="F2" s="13"/>
+      <x:c r="F2" s="16"/>
       <x:c r="G2" s="16"/>
       <x:c r="H2" s="16"/>
       <x:c r="I2" s="17"/>
@@ -652,7 +652,7 @@
       <x:c r="C3" s="13"/>
       <x:c r="D3" s="13"/>
       <x:c r="E3" s="13"/>
-      <x:c r="F3" s="13"/>
+      <x:c r="F3" s="16"/>
       <x:c r="G3" s="16"/>
       <x:c r="H3" s="16"/>
       <x:c r="I3" s="17"/>
@@ -683,7 +683,7 @@
       <x:c r="C4" s="13"/>
       <x:c r="D4" s="13"/>
       <x:c r="E4" s="13"/>
-      <x:c r="F4" s="13"/>
+      <x:c r="F4" s="16"/>
       <x:c r="G4" s="16"/>
       <x:c r="H4" s="16"/>
       <x:c r="I4" s="17"/>
@@ -714,7 +714,7 @@
       <x:c r="C5" s="13"/>
       <x:c r="D5" s="13"/>
       <x:c r="E5" s="13"/>
-      <x:c r="F5" s="13"/>
+      <x:c r="F5" s="16"/>
       <x:c r="G5" s="16"/>
       <x:c r="H5" s="16"/>
       <x:c r="I5" s="17"/>
@@ -745,7 +745,7 @@
       <x:c r="C6" s="13"/>
       <x:c r="D6" s="13"/>
       <x:c r="E6" s="13"/>
-      <x:c r="F6" s="13"/>
+      <x:c r="F6" s="16"/>
       <x:c r="G6" s="16"/>
       <x:c r="H6" s="16"/>
       <x:c r="I6" s="17"/>
@@ -776,7 +776,7 @@
       <x:c r="C7" s="13"/>
       <x:c r="D7" s="13"/>
       <x:c r="E7" s="13"/>
-      <x:c r="F7" s="13"/>
+      <x:c r="F7" s="16"/>
       <x:c r="G7" s="16"/>
       <x:c r="H7" s="16"/>
       <x:c r="I7" s="17"/>
@@ -807,7 +807,7 @@
       <x:c r="C8" s="13"/>
       <x:c r="D8" s="13"/>
       <x:c r="E8" s="13"/>
-      <x:c r="F8" s="13"/>
+      <x:c r="F8" s="16"/>
       <x:c r="G8" s="16"/>
       <x:c r="H8" s="16"/>
       <x:c r="I8" s="17"/>
@@ -838,7 +838,7 @@
       <x:c r="C9" s="13"/>
       <x:c r="D9" s="13"/>
       <x:c r="E9" s="13"/>
-      <x:c r="F9" s="13"/>
+      <x:c r="F9" s="16"/>
       <x:c r="G9" s="16"/>
       <x:c r="H9" s="16"/>
       <x:c r="I9" s="17"/>
@@ -869,7 +869,7 @@
       <x:c r="C10" s="13"/>
       <x:c r="D10" s="13"/>
       <x:c r="E10" s="13"/>
-      <x:c r="F10" s="13"/>
+      <x:c r="F10" s="16"/>
       <x:c r="G10" s="16"/>
       <x:c r="H10" s="16"/>
       <x:c r="I10" s="17"/>
@@ -900,7 +900,7 @@
       <x:c r="C11" s="13"/>
       <x:c r="D11" s="13"/>
       <x:c r="E11" s="13"/>
-      <x:c r="F11" s="13"/>
+      <x:c r="F11" s="16"/>
       <x:c r="G11" s="16"/>
       <x:c r="H11" s="16"/>
       <x:c r="I11" s="17"/>
@@ -931,7 +931,7 @@
       <x:c r="C12" s="13"/>
       <x:c r="D12" s="13"/>
       <x:c r="E12" s="13"/>
-      <x:c r="F12" s="13"/>
+      <x:c r="F12" s="16"/>
       <x:c r="G12" s="16"/>
       <x:c r="H12" s="16"/>
       <x:c r="I12" s="17"/>
@@ -962,7 +962,7 @@
       <x:c r="C13" s="13"/>
       <x:c r="D13" s="13"/>
       <x:c r="E13" s="13"/>
-      <x:c r="F13" s="13"/>
+      <x:c r="F13" s="16"/>
       <x:c r="G13" s="16"/>
       <x:c r="H13" s="16"/>
       <x:c r="I13" s="17"/>
@@ -993,7 +993,7 @@
       <x:c r="C14" s="13"/>
       <x:c r="D14" s="13"/>
       <x:c r="E14" s="13"/>
-      <x:c r="F14" s="13"/>
+      <x:c r="F14" s="16"/>
       <x:c r="G14" s="16"/>
       <x:c r="H14" s="16"/>
       <x:c r="I14" s="17"/>
@@ -1024,7 +1024,7 @@
       <x:c r="C15" s="13"/>
       <x:c r="D15" s="13"/>
       <x:c r="E15" s="13"/>
-      <x:c r="F15" s="13"/>
+      <x:c r="F15" s="16"/>
       <x:c r="G15" s="16"/>
       <x:c r="H15" s="16"/>
       <x:c r="I15" s="17"/>
@@ -1055,7 +1055,7 @@
       <x:c r="C16" s="13"/>
       <x:c r="D16" s="13"/>
       <x:c r="E16" s="13"/>
-      <x:c r="F16" s="13"/>
+      <x:c r="F16" s="16"/>
       <x:c r="G16" s="16"/>
       <x:c r="H16" s="16"/>
       <x:c r="I16" s="17"/>
@@ -1086,7 +1086,7 @@
       <x:c r="C17" s="13"/>
       <x:c r="D17" s="13"/>
       <x:c r="E17" s="13"/>
-      <x:c r="F17" s="13"/>
+      <x:c r="F17" s="16"/>
       <x:c r="G17" s="16"/>
       <x:c r="H17" s="16"/>
       <x:c r="I17" s="17"/>
@@ -1117,7 +1117,7 @@
       <x:c r="C18" s="13"/>
       <x:c r="D18" s="13"/>
       <x:c r="E18" s="13"/>
-      <x:c r="F18" s="13"/>
+      <x:c r="F18" s="16"/>
       <x:c r="G18" s="16"/>
       <x:c r="H18" s="16"/>
       <x:c r="I18" s="17"/>
@@ -1148,7 +1148,7 @@
       <x:c r="C19" s="13"/>
       <x:c r="D19" s="13"/>
       <x:c r="E19" s="13"/>
-      <x:c r="F19" s="13"/>
+      <x:c r="F19" s="16"/>
       <x:c r="G19" s="16"/>
       <x:c r="H19" s="16"/>
       <x:c r="I19" s="17"/>
@@ -1179,7 +1179,7 @@
       <x:c r="C20" s="13"/>
       <x:c r="D20" s="13"/>
       <x:c r="E20" s="13"/>
-      <x:c r="F20" s="13"/>
+      <x:c r="F20" s="16"/>
       <x:c r="G20" s="16"/>
       <x:c r="H20" s="16"/>
       <x:c r="I20" s="17"/>
@@ -1210,7 +1210,7 @@
       <x:c r="C21" s="13"/>
       <x:c r="D21" s="13"/>
       <x:c r="E21" s="13"/>
-      <x:c r="F21" s="13"/>
+      <x:c r="F21" s="16"/>
       <x:c r="G21" s="16"/>
       <x:c r="H21" s="16"/>
       <x:c r="I21" s="17"/>
@@ -1241,7 +1241,7 @@
       <x:c r="C22" s="13"/>
       <x:c r="D22" s="13"/>
       <x:c r="E22" s="13"/>
-      <x:c r="F22" s="13"/>
+      <x:c r="F22" s="16"/>
       <x:c r="G22" s="16"/>
       <x:c r="H22" s="16"/>
       <x:c r="I22" s="17"/>
@@ -1272,7 +1272,7 @@
       <x:c r="C23" s="13"/>
       <x:c r="D23" s="13"/>
       <x:c r="E23" s="13"/>
-      <x:c r="F23" s="13"/>
+      <x:c r="F23" s="16"/>
       <x:c r="G23" s="16"/>
       <x:c r="H23" s="16"/>
       <x:c r="I23" s="17"/>
@@ -1303,7 +1303,7 @@
       <x:c r="C24" s="13"/>
       <x:c r="D24" s="13"/>
       <x:c r="E24" s="13"/>
-      <x:c r="F24" s="13"/>
+      <x:c r="F24" s="16"/>
       <x:c r="G24" s="16"/>
       <x:c r="H24" s="16"/>
       <x:c r="I24" s="17"/>
@@ -1334,7 +1334,7 @@
       <x:c r="C25" s="13"/>
       <x:c r="D25" s="13"/>
       <x:c r="E25" s="13"/>
-      <x:c r="F25" s="13"/>
+      <x:c r="F25" s="16"/>
       <x:c r="G25" s="16"/>
       <x:c r="H25" s="16"/>
       <x:c r="I25" s="17"/>
@@ -1365,7 +1365,7 @@
       <x:c r="C26" s="13"/>
       <x:c r="D26" s="13"/>
       <x:c r="E26" s="13"/>
-      <x:c r="F26" s="13"/>
+      <x:c r="F26" s="16"/>
       <x:c r="G26" s="16"/>
       <x:c r="H26" s="16"/>
       <x:c r="I26" s="17"/>
@@ -1396,7 +1396,7 @@
       <x:c r="C27" s="13"/>
       <x:c r="D27" s="13"/>
       <x:c r="E27" s="13"/>
-      <x:c r="F27" s="13"/>
+      <x:c r="F27" s="16"/>
       <x:c r="G27" s="16"/>
       <x:c r="H27" s="16"/>
       <x:c r="I27" s="17"/>
@@ -1427,7 +1427,7 @@
       <x:c r="C28" s="13"/>
       <x:c r="D28" s="13"/>
       <x:c r="E28" s="13"/>
-      <x:c r="F28" s="13"/>
+      <x:c r="F28" s="16"/>
       <x:c r="G28" s="16"/>
       <x:c r="H28" s="16"/>
       <x:c r="I28" s="17"/>
@@ -1458,7 +1458,7 @@
       <x:c r="C29" s="13"/>
       <x:c r="D29" s="13"/>
       <x:c r="E29" s="13"/>
-      <x:c r="F29" s="13"/>
+      <x:c r="F29" s="16"/>
       <x:c r="G29" s="16"/>
       <x:c r="H29" s="16"/>
       <x:c r="I29" s="17"/>
@@ -1489,7 +1489,7 @@
       <x:c r="C30" s="13"/>
       <x:c r="D30" s="13"/>
       <x:c r="E30" s="13"/>
-      <x:c r="F30" s="13"/>
+      <x:c r="F30" s="16"/>
       <x:c r="G30" s="16"/>
       <x:c r="H30" s="16"/>
       <x:c r="I30" s="17"/>
@@ -1520,7 +1520,7 @@
       <x:c r="C31" s="13"/>
       <x:c r="D31" s="13"/>
       <x:c r="E31" s="13"/>
-      <x:c r="F31" s="13"/>
+      <x:c r="F31" s="16"/>
       <x:c r="G31" s="16"/>
       <x:c r="H31" s="16"/>
       <x:c r="I31" s="17"/>
@@ -1551,7 +1551,7 @@
       <x:c r="C32" s="13"/>
       <x:c r="D32" s="13"/>
       <x:c r="E32" s="13"/>
-      <x:c r="F32" s="13"/>
+      <x:c r="F32" s="16"/>
       <x:c r="G32" s="16"/>
       <x:c r="H32" s="16"/>
       <x:c r="I32" s="17"/>
@@ -1582,7 +1582,7 @@
       <x:c r="C33" s="13"/>
       <x:c r="D33" s="13"/>
       <x:c r="E33" s="13"/>
-      <x:c r="F33" s="13"/>
+      <x:c r="F33" s="16"/>
       <x:c r="G33" s="16"/>
       <x:c r="H33" s="16"/>
       <x:c r="I33" s="17"/>
@@ -1613,7 +1613,7 @@
       <x:c r="C34" s="13"/>
       <x:c r="D34" s="13"/>
       <x:c r="E34" s="13"/>
-      <x:c r="F34" s="13"/>
+      <x:c r="F34" s="16"/>
       <x:c r="G34" s="16"/>
       <x:c r="H34" s="16"/>
       <x:c r="I34" s="17"/>
@@ -1644,7 +1644,7 @@
       <x:c r="C35" s="13"/>
       <x:c r="D35" s="13"/>
       <x:c r="E35" s="13"/>
-      <x:c r="F35" s="13"/>
+      <x:c r="F35" s="16"/>
       <x:c r="G35" s="16"/>
       <x:c r="H35" s="16"/>
       <x:c r="I35" s="17"/>
@@ -1675,7 +1675,7 @@
       <x:c r="C36" s="13"/>
       <x:c r="D36" s="13"/>
       <x:c r="E36" s="13"/>
-      <x:c r="F36" s="13"/>
+      <x:c r="F36" s="16"/>
       <x:c r="G36" s="16"/>
       <x:c r="H36" s="16"/>
       <x:c r="I36" s="17"/>
@@ -1706,7 +1706,7 @@
       <x:c r="C37" s="13"/>
       <x:c r="D37" s="13"/>
       <x:c r="E37" s="13"/>
-      <x:c r="F37" s="13"/>
+      <x:c r="F37" s="16"/>
       <x:c r="G37" s="16"/>
       <x:c r="H37" s="16"/>
       <x:c r="I37" s="17"/>
@@ -1737,7 +1737,7 @@
       <x:c r="C38" s="13"/>
       <x:c r="D38" s="13"/>
       <x:c r="E38" s="13"/>
-      <x:c r="F38" s="13"/>
+      <x:c r="F38" s="16"/>
       <x:c r="G38" s="16"/>
       <x:c r="H38" s="16"/>
       <x:c r="I38" s="17"/>
@@ -1768,7 +1768,7 @@
       <x:c r="C39" s="13"/>
       <x:c r="D39" s="13"/>
       <x:c r="E39" s="13"/>
-      <x:c r="F39" s="13"/>
+      <x:c r="F39" s="16"/>
       <x:c r="G39" s="16"/>
       <x:c r="H39" s="16"/>
       <x:c r="I39" s="17"/>
@@ -1799,7 +1799,7 @@
       <x:c r="C40" s="13"/>
       <x:c r="D40" s="13"/>
       <x:c r="E40" s="13"/>
-      <x:c r="F40" s="13"/>
+      <x:c r="F40" s="16"/>
       <x:c r="G40" s="16"/>
       <x:c r="H40" s="16"/>
       <x:c r="I40" s="17"/>
@@ -1830,7 +1830,7 @@
       <x:c r="C41" s="13"/>
       <x:c r="D41" s="13"/>
       <x:c r="E41" s="13"/>
-      <x:c r="F41" s="13"/>
+      <x:c r="F41" s="16"/>
       <x:c r="G41" s="16"/>
       <x:c r="H41" s="16"/>
       <x:c r="I41" s="17"/>
@@ -1861,7 +1861,7 @@
       <x:c r="C42" s="13"/>
       <x:c r="D42" s="13"/>
       <x:c r="E42" s="13"/>
-      <x:c r="F42" s="13"/>
+      <x:c r="F42" s="16"/>
       <x:c r="G42" s="16"/>
       <x:c r="H42" s="16"/>
       <x:c r="I42" s="17"/>
@@ -1892,7 +1892,7 @@
       <x:c r="C43" s="13"/>
       <x:c r="D43" s="13"/>
       <x:c r="E43" s="13"/>
-      <x:c r="F43" s="13"/>
+      <x:c r="F43" s="16"/>
       <x:c r="G43" s="16"/>
       <x:c r="H43" s="16"/>
       <x:c r="I43" s="17"/>
@@ -1923,7 +1923,7 @@
       <x:c r="C44" s="13"/>
       <x:c r="D44" s="13"/>
       <x:c r="E44" s="13"/>
-      <x:c r="F44" s="13"/>
+      <x:c r="F44" s="16"/>
       <x:c r="G44" s="16"/>
       <x:c r="H44" s="16"/>
       <x:c r="I44" s="17"/>
@@ -1954,7 +1954,7 @@
       <x:c r="C45" s="13"/>
       <x:c r="D45" s="13"/>
       <x:c r="E45" s="13"/>
-      <x:c r="F45" s="13"/>
+      <x:c r="F45" s="16"/>
       <x:c r="G45" s="16"/>
       <x:c r="H45" s="16"/>
       <x:c r="I45" s="17"/>
@@ -1985,7 +1985,7 @@
       <x:c r="C46" s="13"/>
       <x:c r="D46" s="13"/>
       <x:c r="E46" s="13"/>
-      <x:c r="F46" s="13"/>
+      <x:c r="F46" s="16"/>
       <x:c r="G46" s="16"/>
       <x:c r="H46" s="16"/>
       <x:c r="I46" s="17"/>
@@ -2016,7 +2016,7 @@
       <x:c r="C47" s="13"/>
       <x:c r="D47" s="13"/>
       <x:c r="E47" s="13"/>
-      <x:c r="F47" s="13"/>
+      <x:c r="F47" s="16"/>
       <x:c r="G47" s="16"/>
       <x:c r="H47" s="16"/>
       <x:c r="I47" s="17"/>
@@ -2047,7 +2047,7 @@
       <x:c r="C48" s="13"/>
       <x:c r="D48" s="13"/>
       <x:c r="E48" s="13"/>
-      <x:c r="F48" s="13"/>
+      <x:c r="F48" s="16"/>
       <x:c r="G48" s="16"/>
       <x:c r="H48" s="16"/>
       <x:c r="I48" s="17"/>
@@ -2078,7 +2078,7 @@
       <x:c r="C49" s="13"/>
       <x:c r="D49" s="13"/>
       <x:c r="E49" s="13"/>
-      <x:c r="F49" s="13"/>
+      <x:c r="F49" s="16"/>
       <x:c r="G49" s="16"/>
       <x:c r="H49" s="16"/>
       <x:c r="I49" s="17"/>
@@ -2109,7 +2109,7 @@
       <x:c r="C50" s="13"/>
       <x:c r="D50" s="13"/>
       <x:c r="E50" s="13"/>
-      <x:c r="F50" s="13"/>
+      <x:c r="F50" s="16"/>
       <x:c r="G50" s="16"/>
       <x:c r="H50" s="16"/>
       <x:c r="I50" s="17"/>
@@ -2140,7 +2140,7 @@
       <x:c r="C51" s="13"/>
       <x:c r="D51" s="13"/>
       <x:c r="E51" s="13"/>
-      <x:c r="F51" s="13"/>
+      <x:c r="F51" s="16"/>
       <x:c r="G51" s="16"/>
       <x:c r="H51" s="16"/>
       <x:c r="I51" s="17"/>
@@ -2171,7 +2171,7 @@
       <x:c r="C52" s="13"/>
       <x:c r="D52" s="13"/>
       <x:c r="E52" s="13"/>
-      <x:c r="F52" s="13"/>
+      <x:c r="F52" s="16"/>
       <x:c r="G52" s="16"/>
       <x:c r="H52" s="16"/>
       <x:c r="I52" s="17"/>
@@ -2202,7 +2202,7 @@
       <x:c r="C53" s="13"/>
       <x:c r="D53" s="13"/>
       <x:c r="E53" s="13"/>
-      <x:c r="F53" s="13"/>
+      <x:c r="F53" s="16"/>
       <x:c r="G53" s="16"/>
       <x:c r="H53" s="16"/>
       <x:c r="I53" s="17"/>
@@ -2233,7 +2233,7 @@
       <x:c r="C54" s="13"/>
       <x:c r="D54" s="13"/>
       <x:c r="E54" s="13"/>
-      <x:c r="F54" s="13"/>
+      <x:c r="F54" s="16"/>
       <x:c r="G54" s="16"/>
       <x:c r="H54" s="16"/>
       <x:c r="I54" s="17"/>
@@ -2264,7 +2264,7 @@
       <x:c r="C55" s="13"/>
       <x:c r="D55" s="13"/>
       <x:c r="E55" s="13"/>
-      <x:c r="F55" s="13"/>
+      <x:c r="F55" s="16"/>
       <x:c r="G55" s="16"/>
       <x:c r="H55" s="16"/>
       <x:c r="I55" s="17"/>
@@ -2295,7 +2295,7 @@
       <x:c r="C56" s="13"/>
       <x:c r="D56" s="13"/>
       <x:c r="E56" s="13"/>
-      <x:c r="F56" s="13"/>
+      <x:c r="F56" s="16"/>
       <x:c r="G56" s="16"/>
       <x:c r="H56" s="16"/>
       <x:c r="I56" s="17"/>
@@ -2326,7 +2326,7 @@
       <x:c r="C57" s="13"/>
       <x:c r="D57" s="13"/>
       <x:c r="E57" s="13"/>
-      <x:c r="F57" s="13"/>
+      <x:c r="F57" s="16"/>
       <x:c r="G57" s="16"/>
       <x:c r="H57" s="16"/>
       <x:c r="I57" s="17"/>
@@ -2357,7 +2357,7 @@
       <x:c r="C58" s="13"/>
       <x:c r="D58" s="13"/>
       <x:c r="E58" s="13"/>
-      <x:c r="F58" s="13"/>
+      <x:c r="F58" s="16"/>
       <x:c r="G58" s="16"/>
       <x:c r="H58" s="16"/>
       <x:c r="I58" s="17"/>
@@ -2388,7 +2388,7 @@
       <x:c r="C59" s="13"/>
       <x:c r="D59" s="13"/>
       <x:c r="E59" s="13"/>
-      <x:c r="F59" s="13"/>
+      <x:c r="F59" s="16"/>
       <x:c r="G59" s="16"/>
       <x:c r="H59" s="16"/>
       <x:c r="I59" s="17"/>
@@ -2419,7 +2419,7 @@
       <x:c r="C60" s="13"/>
       <x:c r="D60" s="13"/>
       <x:c r="E60" s="13"/>
-      <x:c r="F60" s="13"/>
+      <x:c r="F60" s="16"/>
       <x:c r="G60" s="16"/>
       <x:c r="H60" s="16"/>
       <x:c r="I60" s="17"/>
@@ -2450,7 +2450,7 @@
       <x:c r="C61" s="13"/>
       <x:c r="D61" s="13"/>
       <x:c r="E61" s="13"/>
-      <x:c r="F61" s="13"/>
+      <x:c r="F61" s="16"/>
       <x:c r="G61" s="16"/>
       <x:c r="H61" s="16"/>
       <x:c r="I61" s="17"/>
@@ -2481,7 +2481,7 @@
       <x:c r="C62" s="13"/>
       <x:c r="D62" s="13"/>
       <x:c r="E62" s="13"/>
-      <x:c r="F62" s="13"/>
+      <x:c r="F62" s="16"/>
       <x:c r="G62" s="16"/>
       <x:c r="H62" s="16"/>
       <x:c r="I62" s="17"/>
@@ -2512,7 +2512,7 @@
       <x:c r="C63" s="13"/>
       <x:c r="D63" s="13"/>
       <x:c r="E63" s="13"/>
-      <x:c r="F63" s="13"/>
+      <x:c r="F63" s="16"/>
       <x:c r="G63" s="16"/>
       <x:c r="H63" s="16"/>
       <x:c r="I63" s="17"/>
@@ -2543,7 +2543,7 @@
       <x:c r="C64" s="13"/>
       <x:c r="D64" s="13"/>
       <x:c r="E64" s="13"/>
-      <x:c r="F64" s="13"/>
+      <x:c r="F64" s="16"/>
       <x:c r="G64" s="16"/>
       <x:c r="H64" s="16"/>
       <x:c r="I64" s="17"/>
@@ -2574,7 +2574,7 @@
       <x:c r="C65" s="13"/>
       <x:c r="D65" s="13"/>
       <x:c r="E65" s="13"/>
-      <x:c r="F65" s="13"/>
+      <x:c r="F65" s="16"/>
       <x:c r="G65" s="16"/>
       <x:c r="H65" s="16"/>
       <x:c r="I65" s="17"/>
@@ -2605,7 +2605,7 @@
       <x:c r="C66" s="13"/>
       <x:c r="D66" s="13"/>
       <x:c r="E66" s="13"/>
-      <x:c r="F66" s="13"/>
+      <x:c r="F66" s="16"/>
       <x:c r="G66" s="16"/>
       <x:c r="H66" s="16"/>
       <x:c r="I66" s="17"/>
@@ -2636,7 +2636,7 @@
       <x:c r="C67" s="13"/>
       <x:c r="D67" s="13"/>
       <x:c r="E67" s="13"/>
-      <x:c r="F67" s="13"/>
+      <x:c r="F67" s="16"/>
       <x:c r="G67" s="16"/>
       <x:c r="H67" s="16"/>
       <x:c r="I67" s="17"/>
@@ -2667,7 +2667,7 @@
       <x:c r="C68" s="13"/>
       <x:c r="D68" s="13"/>
       <x:c r="E68" s="13"/>
-      <x:c r="F68" s="13"/>
+      <x:c r="F68" s="16"/>
       <x:c r="G68" s="16"/>
       <x:c r="H68" s="16"/>
       <x:c r="I68" s="17"/>
@@ -2698,7 +2698,7 @@
       <x:c r="C69" s="13"/>
       <x:c r="D69" s="13"/>
       <x:c r="E69" s="13"/>
-      <x:c r="F69" s="13"/>
+      <x:c r="F69" s="16"/>
       <x:c r="G69" s="16"/>
       <x:c r="H69" s="16"/>
       <x:c r="I69" s="17"/>
@@ -2729,7 +2729,7 @@
       <x:c r="C70" s="13"/>
       <x:c r="D70" s="13"/>
       <x:c r="E70" s="13"/>
-      <x:c r="F70" s="13"/>
+      <x:c r="F70" s="16"/>
       <x:c r="G70" s="16"/>
       <x:c r="H70" s="16"/>
       <x:c r="I70" s="17"/>
@@ -2760,7 +2760,7 @@
       <x:c r="C71" s="13"/>
       <x:c r="D71" s="13"/>
       <x:c r="E71" s="13"/>
-      <x:c r="F71" s="13"/>
+      <x:c r="F71" s="16"/>
       <x:c r="G71" s="16"/>
       <x:c r="H71" s="16"/>
       <x:c r="I71" s="17"/>
@@ -2791,7 +2791,7 @@
       <x:c r="C72" s="13"/>
       <x:c r="D72" s="13"/>
       <x:c r="E72" s="13"/>
-      <x:c r="F72" s="13"/>
+      <x:c r="F72" s="16"/>
       <x:c r="G72" s="16"/>
       <x:c r="H72" s="16"/>
       <x:c r="I72" s="17"/>
@@ -2822,7 +2822,7 @@
       <x:c r="C73" s="13"/>
       <x:c r="D73" s="13"/>
       <x:c r="E73" s="13"/>
-      <x:c r="F73" s="13"/>
+      <x:c r="F73" s="16"/>
       <x:c r="G73" s="16"/>
       <x:c r="H73" s="16"/>
       <x:c r="I73" s="17"/>
@@ -2853,7 +2853,7 @@
       <x:c r="C74" s="13"/>
       <x:c r="D74" s="13"/>
       <x:c r="E74" s="13"/>
-      <x:c r="F74" s="13"/>
+      <x:c r="F74" s="16"/>
       <x:c r="G74" s="16"/>
       <x:c r="H74" s="16"/>
       <x:c r="I74" s="17"/>
@@ -2884,7 +2884,7 @@
       <x:c r="C75" s="13"/>
       <x:c r="D75" s="13"/>
       <x:c r="E75" s="13"/>
-      <x:c r="F75" s="13"/>
+      <x:c r="F75" s="16"/>
       <x:c r="G75" s="16"/>
       <x:c r="H75" s="16"/>
       <x:c r="I75" s="17"/>
@@ -2915,7 +2915,7 @@
       <x:c r="C76" s="13"/>
       <x:c r="D76" s="13"/>
       <x:c r="E76" s="13"/>
-      <x:c r="F76" s="13"/>
+      <x:c r="F76" s="16"/>
       <x:c r="G76" s="16"/>
       <x:c r="H76" s="16"/>
       <x:c r="I76" s="17"/>
@@ -2946,7 +2946,7 @@
       <x:c r="C77" s="13"/>
       <x:c r="D77" s="13"/>
       <x:c r="E77" s="13"/>
-      <x:c r="F77" s="13"/>
+      <x:c r="F77" s="16"/>
       <x:c r="G77" s="16"/>
       <x:c r="H77" s="16"/>
       <x:c r="I77" s="17"/>
@@ -2977,7 +2977,7 @@
       <x:c r="C78" s="13"/>
       <x:c r="D78" s="13"/>
       <x:c r="E78" s="13"/>
-      <x:c r="F78" s="13"/>
+      <x:c r="F78" s="16"/>
       <x:c r="G78" s="16"/>
       <x:c r="H78" s="16"/>
       <x:c r="I78" s="17"/>
@@ -3008,7 +3008,7 @@
       <x:c r="C79" s="13"/>
       <x:c r="D79" s="13"/>
       <x:c r="E79" s="13"/>
-      <x:c r="F79" s="13"/>
+      <x:c r="F79" s="16"/>
       <x:c r="G79" s="16"/>
       <x:c r="H79" s="16"/>
       <x:c r="I79" s="17"/>
@@ -3039,7 +3039,7 @@
       <x:c r="C80" s="13"/>
       <x:c r="D80" s="13"/>
       <x:c r="E80" s="13"/>
-      <x:c r="F80" s="13"/>
+      <x:c r="F80" s="16"/>
       <x:c r="G80" s="16"/>
       <x:c r="H80" s="16"/>
       <x:c r="I80" s="17"/>
@@ -3070,7 +3070,7 @@
       <x:c r="C81" s="13"/>
       <x:c r="D81" s="13"/>
       <x:c r="E81" s="13"/>
-      <x:c r="F81" s="13"/>
+      <x:c r="F81" s="16"/>
       <x:c r="G81" s="16"/>
       <x:c r="H81" s="16"/>
       <x:c r="I81" s="17"/>
@@ -3101,7 +3101,7 @@
       <x:c r="C82" s="13"/>
       <x:c r="D82" s="13"/>
       <x:c r="E82" s="13"/>
-      <x:c r="F82" s="13"/>
+      <x:c r="F82" s="16"/>
       <x:c r="G82" s="16"/>
       <x:c r="H82" s="16"/>
       <x:c r="I82" s="17"/>
@@ -3132,7 +3132,7 @@
       <x:c r="C83" s="13"/>
       <x:c r="D83" s="13"/>
       <x:c r="E83" s="13"/>
-      <x:c r="F83" s="13"/>
+      <x:c r="F83" s="16"/>
       <x:c r="G83" s="16"/>
       <x:c r="H83" s="16"/>
       <x:c r="I83" s="17"/>
@@ -3163,7 +3163,7 @@
       <x:c r="C84" s="13"/>
       <x:c r="D84" s="13"/>
       <x:c r="E84" s="13"/>
-      <x:c r="F84" s="13"/>
+      <x:c r="F84" s="16"/>
       <x:c r="G84" s="16"/>
       <x:c r="H84" s="16"/>
       <x:c r="I84" s="17"/>
@@ -3194,7 +3194,7 @@
       <x:c r="C85" s="13"/>
       <x:c r="D85" s="13"/>
       <x:c r="E85" s="13"/>
-      <x:c r="F85" s="13"/>
+      <x:c r="F85" s="16"/>
       <x:c r="G85" s="16"/>
       <x:c r="H85" s="16"/>
       <x:c r="I85" s="17"/>
@@ -3225,7 +3225,7 @@
       <x:c r="C86" s="13"/>
       <x:c r="D86" s="13"/>
       <x:c r="E86" s="13"/>
-      <x:c r="F86" s="13"/>
+      <x:c r="F86" s="16"/>
       <x:c r="G86" s="16"/>
       <x:c r="H86" s="16"/>
       <x:c r="I86" s="17"/>
@@ -3256,7 +3256,7 @@
       <x:c r="C87" s="13"/>
       <x:c r="D87" s="13"/>
       <x:c r="E87" s="13"/>
-      <x:c r="F87" s="13"/>
+      <x:c r="F87" s="16"/>
       <x:c r="G87" s="16"/>
       <x:c r="H87" s="16"/>
       <x:c r="I87" s="17"/>
@@ -3287,7 +3287,7 @@
       <x:c r="C88" s="13"/>
       <x:c r="D88" s="13"/>
       <x:c r="E88" s="13"/>
-      <x:c r="F88" s="13"/>
+      <x:c r="F88" s="16"/>
       <x:c r="G88" s="16"/>
       <x:c r="H88" s="16"/>
       <x:c r="I88" s="17"/>
@@ -3318,7 +3318,7 @@
       <x:c r="C89" s="13"/>
       <x:c r="D89" s="13"/>
       <x:c r="E89" s="13"/>
-      <x:c r="F89" s="13"/>
+      <x:c r="F89" s="16"/>
       <x:c r="G89" s="16"/>
       <x:c r="H89" s="16"/>
       <x:c r="I89" s="17"/>
@@ -3349,7 +3349,7 @@
       <x:c r="C90" s="13"/>
       <x:c r="D90" s="13"/>
       <x:c r="E90" s="13"/>
-      <x:c r="F90" s="13"/>
+      <x:c r="F90" s="16"/>
       <x:c r="G90" s="16"/>
       <x:c r="H90" s="16"/>
       <x:c r="I90" s="17"/>
@@ -3380,7 +3380,7 @@
       <x:c r="C91" s="13"/>
       <x:c r="D91" s="13"/>
       <x:c r="E91" s="13"/>
-      <x:c r="F91" s="13"/>
+      <x:c r="F91" s="16"/>
       <x:c r="G91" s="16"/>
       <x:c r="H91" s="16"/>
       <x:c r="I91" s="17"/>
@@ -3411,7 +3411,7 @@
       <x:c r="C92" s="13"/>
       <x:c r="D92" s="13"/>
       <x:c r="E92" s="13"/>
-      <x:c r="F92" s="13"/>
+      <x:c r="F92" s="16"/>
       <x:c r="G92" s="16"/>
       <x:c r="H92" s="16"/>
       <x:c r="I92" s="17"/>
@@ -3442,7 +3442,7 @@
       <x:c r="C93" s="13"/>
       <x:c r="D93" s="13"/>
       <x:c r="E93" s="13"/>
-      <x:c r="F93" s="13"/>
+      <x:c r="F93" s="16"/>
       <x:c r="G93" s="16"/>
       <x:c r="H93" s="16"/>
       <x:c r="I93" s="17"/>
@@ -3473,7 +3473,7 @@
       <x:c r="C94" s="13"/>
       <x:c r="D94" s="13"/>
       <x:c r="E94" s="13"/>
-      <x:c r="F94" s="13"/>
+      <x:c r="F94" s="16"/>
       <x:c r="G94" s="16"/>
       <x:c r="H94" s="16"/>
       <x:c r="I94" s="17"/>
@@ -3504,7 +3504,7 @@
       <x:c r="C95" s="13"/>
       <x:c r="D95" s="13"/>
       <x:c r="E95" s="13"/>
-      <x:c r="F95" s="13"/>
+      <x:c r="F95" s="16"/>
       <x:c r="G95" s="16"/>
       <x:c r="H95" s="16"/>
       <x:c r="I95" s="17"/>
@@ -3535,7 +3535,7 @@
       <x:c r="C96" s="13"/>
       <x:c r="D96" s="13"/>
       <x:c r="E96" s="13"/>
-      <x:c r="F96" s="13"/>
+      <x:c r="F96" s="16"/>
       <x:c r="G96" s="16"/>
       <x:c r="H96" s="16"/>
       <x:c r="I96" s="17"/>
@@ -3566,7 +3566,7 @@
       <x:c r="C97" s="13"/>
       <x:c r="D97" s="13"/>
       <x:c r="E97" s="13"/>
-      <x:c r="F97" s="13"/>
+      <x:c r="F97" s="16"/>
       <x:c r="G97" s="16"/>
       <x:c r="H97" s="16"/>
       <x:c r="I97" s="17"/>
@@ -3597,7 +3597,7 @@
       <x:c r="C98" s="13"/>
       <x:c r="D98" s="13"/>
       <x:c r="E98" s="13"/>
-      <x:c r="F98" s="13"/>
+      <x:c r="F98" s="16"/>
       <x:c r="G98" s="16"/>
       <x:c r="H98" s="16"/>
       <x:c r="I98" s="17"/>
@@ -3628,7 +3628,7 @@
       <x:c r="C99" s="13"/>
       <x:c r="D99" s="13"/>
       <x:c r="E99" s="13"/>
-      <x:c r="F99" s="13"/>
+      <x:c r="F99" s="16"/>
       <x:c r="G99" s="16"/>
       <x:c r="H99" s="16"/>
       <x:c r="I99" s="17"/>
@@ -3659,7 +3659,7 @@
       <x:c r="C100" s="13"/>
       <x:c r="D100" s="13"/>
       <x:c r="E100" s="13"/>
-      <x:c r="F100" s="13"/>
+      <x:c r="F100" s="16"/>
       <x:c r="G100" s="16"/>
       <x:c r="H100" s="16"/>
       <x:c r="I100" s="17"/>
@@ -3690,7 +3690,7 @@
       <x:c r="C101" s="13"/>
       <x:c r="D101" s="13"/>
       <x:c r="E101" s="13"/>
-      <x:c r="F101" s="13"/>
+      <x:c r="F101" s="16"/>
       <x:c r="G101" s="16"/>
       <x:c r="H101" s="16"/>
       <x:c r="I101" s="17"/>
@@ -3721,7 +3721,7 @@
       <x:c r="C102" s="13"/>
       <x:c r="D102" s="13"/>
       <x:c r="E102" s="13"/>
-      <x:c r="F102" s="13"/>
+      <x:c r="F102" s="16"/>
       <x:c r="G102" s="16"/>
       <x:c r="H102" s="16"/>
       <x:c r="I102" s="17"/>
@@ -3752,7 +3752,7 @@
       <x:c r="C103" s="13"/>
       <x:c r="D103" s="13"/>
       <x:c r="E103" s="13"/>
-      <x:c r="F103" s="13"/>
+      <x:c r="F103" s="16"/>
       <x:c r="G103" s="16"/>
       <x:c r="H103" s="16"/>
       <x:c r="I103" s="17"/>
@@ -3783,7 +3783,7 @@
       <x:c r="C104" s="13"/>
       <x:c r="D104" s="13"/>
       <x:c r="E104" s="13"/>
-      <x:c r="F104" s="13"/>
+      <x:c r="F104" s="16"/>
       <x:c r="G104" s="16"/>
       <x:c r="H104" s="16"/>
       <x:c r="I104" s="17"/>
@@ -3814,7 +3814,7 @@
       <x:c r="C105" s="13"/>
       <x:c r="D105" s="13"/>
       <x:c r="E105" s="13"/>
-      <x:c r="F105" s="13"/>
+      <x:c r="F105" s="16"/>
       <x:c r="G105" s="16"/>
       <x:c r="H105" s="16"/>
       <x:c r="I105" s="17"/>
@@ -3845,7 +3845,7 @@
       <x:c r="C106" s="13"/>
       <x:c r="D106" s="13"/>
       <x:c r="E106" s="13"/>
-      <x:c r="F106" s="13"/>
+      <x:c r="F106" s="16"/>
       <x:c r="G106" s="16"/>
       <x:c r="H106" s="16"/>
       <x:c r="I106" s="17"/>
@@ -3876,7 +3876,7 @@
       <x:c r="C107" s="13"/>
       <x:c r="D107" s="13"/>
       <x:c r="E107" s="13"/>
-      <x:c r="F107" s="13"/>
+      <x:c r="F107" s="16"/>
       <x:c r="G107" s="16"/>
       <x:c r="H107" s="16"/>
       <x:c r="I107" s="17"/>
@@ -3907,7 +3907,7 @@
       <x:c r="C108" s="13"/>
       <x:c r="D108" s="13"/>
       <x:c r="E108" s="13"/>
-      <x:c r="F108" s="13"/>
+      <x:c r="F108" s="16"/>
       <x:c r="G108" s="16"/>
       <x:c r="H108" s="16"/>
       <x:c r="I108" s="17"/>
@@ -3938,7 +3938,7 @@
       <x:c r="C109" s="13"/>
       <x:c r="D109" s="13"/>
       <x:c r="E109" s="13"/>
-      <x:c r="F109" s="13"/>
+      <x:c r="F109" s="16"/>
       <x:c r="G109" s="16"/>
       <x:c r="H109" s="16"/>
       <x:c r="I109" s="17"/>
@@ -3969,7 +3969,7 @@
       <x:c r="C110" s="13"/>
       <x:c r="D110" s="13"/>
       <x:c r="E110" s="13"/>
-      <x:c r="F110" s="13"/>
+      <x:c r="F110" s="16"/>
       <x:c r="G110" s="16"/>
       <x:c r="H110" s="16"/>
       <x:c r="I110" s="17"/>
@@ -4000,7 +4000,7 @@
       <x:c r="C111" s="13"/>
       <x:c r="D111" s="13"/>
       <x:c r="E111" s="13"/>
-      <x:c r="F111" s="13"/>
+      <x:c r="F111" s="16"/>
       <x:c r="G111" s="16"/>
       <x:c r="H111" s="16"/>
       <x:c r="I111" s="17"/>
@@ -4031,7 +4031,7 @@
       <x:c r="C112" s="13"/>
       <x:c r="D112" s="13"/>
       <x:c r="E112" s="13"/>
-      <x:c r="F112" s="13"/>
+      <x:c r="F112" s="16"/>
       <x:c r="G112" s="16"/>
       <x:c r="H112" s="16"/>
       <x:c r="I112" s="17"/>
@@ -4062,7 +4062,7 @@
       <x:c r="C113" s="13"/>
       <x:c r="D113" s="13"/>
       <x:c r="E113" s="13"/>
-      <x:c r="F113" s="13"/>
+      <x:c r="F113" s="16"/>
       <x:c r="G113" s="16"/>
       <x:c r="H113" s="16"/>
       <x:c r="I113" s="17"/>
@@ -4093,7 +4093,7 @@
       <x:c r="C114" s="13"/>
       <x:c r="D114" s="13"/>
       <x:c r="E114" s="13"/>
-      <x:c r="F114" s="13"/>
+      <x:c r="F114" s="16"/>
       <x:c r="G114" s="16"/>
       <x:c r="H114" s="16"/>
       <x:c r="I114" s="17"/>
@@ -4124,7 +4124,7 @@
       <x:c r="C115" s="13"/>
       <x:c r="D115" s="13"/>
       <x:c r="E115" s="13"/>
-      <x:c r="F115" s="13"/>
+      <x:c r="F115" s="16"/>
       <x:c r="G115" s="16"/>
       <x:c r="H115" s="16"/>
       <x:c r="I115" s="17"/>
@@ -4155,7 +4155,7 @@
       <x:c r="C116" s="13"/>
       <x:c r="D116" s="13"/>
       <x:c r="E116" s="13"/>
-      <x:c r="F116" s="13"/>
+      <x:c r="F116" s="16"/>
       <x:c r="G116" s="16"/>
       <x:c r="H116" s="16"/>
       <x:c r="I116" s="17"/>
@@ -4186,7 +4186,7 @@
       <x:c r="C117" s="13"/>
       <x:c r="D117" s="13"/>
       <x:c r="E117" s="13"/>
-      <x:c r="F117" s="13"/>
+      <x:c r="F117" s="16"/>
       <x:c r="G117" s="16"/>
       <x:c r="H117" s="16"/>
       <x:c r="I117" s="17"/>
@@ -4217,7 +4217,7 @@
       <x:c r="C118" s="13"/>
       <x:c r="D118" s="13"/>
       <x:c r="E118" s="13"/>
-      <x:c r="F118" s="13"/>
+      <x:c r="F118" s="16"/>
       <x:c r="G118" s="16"/>
       <x:c r="H118" s="16"/>
       <x:c r="I118" s="17"/>
@@ -4248,7 +4248,7 @@
       <x:c r="C119" s="13"/>
       <x:c r="D119" s="13"/>
       <x:c r="E119" s="13"/>
-      <x:c r="F119" s="13"/>
+      <x:c r="F119" s="16"/>
       <x:c r="G119" s="16"/>
       <x:c r="H119" s="16"/>
       <x:c r="I119" s="17"/>
@@ -4279,7 +4279,7 @@
       <x:c r="C120" s="13"/>
       <x:c r="D120" s="13"/>
       <x:c r="E120" s="13"/>
-      <x:c r="F120" s="13"/>
+      <x:c r="F120" s="16"/>
       <x:c r="G120" s="16"/>
       <x:c r="H120" s="16"/>
       <x:c r="I120" s="17"/>
@@ -4310,7 +4310,7 @@
       <x:c r="C121" s="13"/>
       <x:c r="D121" s="13"/>
       <x:c r="E121" s="13"/>
-      <x:c r="F121" s="13"/>
+      <x:c r="F121" s="16"/>
       <x:c r="G121" s="16"/>
       <x:c r="H121" s="16"/>
       <x:c r="I121" s="17"/>
@@ -4341,7 +4341,7 @@
       <x:c r="C122" s="13"/>
       <x:c r="D122" s="13"/>
       <x:c r="E122" s="13"/>
-      <x:c r="F122" s="13"/>
+      <x:c r="F122" s="16"/>
       <x:c r="G122" s="16"/>
       <x:c r="H122" s="16"/>
       <x:c r="I122" s="17"/>
@@ -4372,7 +4372,7 @@
       <x:c r="C123" s="13"/>
       <x:c r="D123" s="13"/>
       <x:c r="E123" s="13"/>
-      <x:c r="F123" s="13"/>
+      <x:c r="F123" s="16"/>
       <x:c r="G123" s="16"/>
       <x:c r="H123" s="16"/>
       <x:c r="I123" s="17"/>
@@ -4403,7 +4403,7 @@
       <x:c r="C124" s="13"/>
       <x:c r="D124" s="13"/>
       <x:c r="E124" s="13"/>
-      <x:c r="F124" s="13"/>
+      <x:c r="F124" s="16"/>
       <x:c r="G124" s="16"/>
       <x:c r="H124" s="16"/>
       <x:c r="I124" s="17"/>
@@ -4434,7 +4434,7 @@
       <x:c r="C125" s="13"/>
       <x:c r="D125" s="13"/>
       <x:c r="E125" s="13"/>
-      <x:c r="F125" s="13"/>
+      <x:c r="F125" s="16"/>
       <x:c r="G125" s="16"/>
       <x:c r="H125" s="16"/>
       <x:c r="I125" s="17"/>
@@ -4465,7 +4465,7 @@
       <x:c r="C126" s="13"/>
       <x:c r="D126" s="13"/>
       <x:c r="E126" s="13"/>
-      <x:c r="F126" s="13"/>
+      <x:c r="F126" s="16"/>
       <x:c r="G126" s="16"/>
       <x:c r="H126" s="16"/>
       <x:c r="I126" s="17"/>
@@ -4496,7 +4496,7 @@
       <x:c r="C127" s="13"/>
       <x:c r="D127" s="13"/>
       <x:c r="E127" s="13"/>
-      <x:c r="F127" s="13"/>
+      <x:c r="F127" s="16"/>
       <x:c r="G127" s="16"/>
       <x:c r="H127" s="16"/>
       <x:c r="I127" s="17"/>
@@ -4527,7 +4527,7 @@
       <x:c r="C128" s="13"/>
       <x:c r="D128" s="13"/>
       <x:c r="E128" s="13"/>
-      <x:c r="F128" s="13"/>
+      <x:c r="F128" s="16"/>
       <x:c r="G128" s="16"/>
       <x:c r="H128" s="16"/>
       <x:c r="I128" s="17"/>
@@ -4558,7 +4558,7 @@
       <x:c r="C129" s="13"/>
       <x:c r="D129" s="13"/>
       <x:c r="E129" s="13"/>
-      <x:c r="F129" s="13"/>
+      <x:c r="F129" s="16"/>
       <x:c r="G129" s="16"/>
       <x:c r="H129" s="16"/>
       <x:c r="I129" s="17"/>
@@ -4589,7 +4589,7 @@
       <x:c r="C130" s="13"/>
       <x:c r="D130" s="13"/>
       <x:c r="E130" s="13"/>
-      <x:c r="F130" s="13"/>
+      <x:c r="F130" s="16"/>
       <x:c r="G130" s="16"/>
       <x:c r="H130" s="16"/>
       <x:c r="I130" s="17"/>
@@ -4620,7 +4620,7 @@
       <x:c r="C131" s="13"/>
       <x:c r="D131" s="13"/>
       <x:c r="E131" s="13"/>
-      <x:c r="F131" s="13"/>
+      <x:c r="F131" s="16"/>
       <x:c r="G131" s="16"/>
       <x:c r="H131" s="16"/>
       <x:c r="I131" s="17"/>
@@ -4651,7 +4651,7 @@
       <x:c r="C132" s="13"/>
       <x:c r="D132" s="13"/>
       <x:c r="E132" s="13"/>
-      <x:c r="F132" s="13"/>
+      <x:c r="F132" s="16"/>
       <x:c r="G132" s="16"/>
       <x:c r="H132" s="16"/>
       <x:c r="I132" s="17"/>
@@ -4682,7 +4682,7 @@
       <x:c r="C133" s="13"/>
       <x:c r="D133" s="13"/>
       <x:c r="E133" s="13"/>
-      <x:c r="F133" s="13"/>
+      <x:c r="F133" s="16"/>
       <x:c r="G133" s="16"/>
       <x:c r="H133" s="16"/>
       <x:c r="I133" s="17"/>
@@ -4713,7 +4713,7 @@
       <x:c r="C134" s="13"/>
       <x:c r="D134" s="13"/>
       <x:c r="E134" s="13"/>
-      <x:c r="F134" s="13"/>
+      <x:c r="F134" s="16"/>
       <x:c r="G134" s="16"/>
       <x:c r="H134" s="16"/>
       <x:c r="I134" s="17"/>
@@ -4744,7 +4744,7 @@
       <x:c r="C135" s="13"/>
       <x:c r="D135" s="13"/>
       <x:c r="E135" s="13"/>
-      <x:c r="F135" s="13"/>
+      <x:c r="F135" s="16"/>
       <x:c r="G135" s="16"/>
       <x:c r="H135" s="16"/>
       <x:c r="I135" s="17"/>
@@ -4775,7 +4775,7 @@
       <x:c r="C136" s="13"/>
       <x:c r="D136" s="13"/>
       <x:c r="E136" s="13"/>
-      <x:c r="F136" s="13"/>
+      <x:c r="F136" s="16"/>
       <x:c r="G136" s="16"/>
       <x:c r="H136" s="16"/>
       <x:c r="I136" s="17"/>
@@ -4806,7 +4806,7 @@
       <x:c r="C137" s="13"/>
       <x:c r="D137" s="13"/>
       <x:c r="E137" s="13"/>
-      <x:c r="F137" s="13"/>
+      <x:c r="F137" s="16"/>
       <x:c r="G137" s="16"/>
       <x:c r="H137" s="16"/>
       <x:c r="I137" s="17"/>
@@ -4837,7 +4837,7 @@
       <x:c r="C138" s="13"/>
       <x:c r="D138" s="13"/>
       <x:c r="E138" s="13"/>
-      <x:c r="F138" s="13"/>
+      <x:c r="F138" s="16"/>
       <x:c r="G138" s="16"/>
       <x:c r="H138" s="16"/>
       <x:c r="I138" s="17"/>
@@ -4868,7 +4868,7 @@
       <x:c r="C139" s="13"/>
       <x:c r="D139" s="13"/>
       <x:c r="E139" s="13"/>
-      <x:c r="F139" s="13"/>
+      <x:c r="F139" s="16"/>
       <x:c r="G139" s="16"/>
       <x:c r="H139" s="16"/>
       <x:c r="I139" s="17"/>
@@ -4899,7 +4899,7 @@
       <x:c r="C140" s="13"/>
       <x:c r="D140" s="13"/>
       <x:c r="E140" s="13"/>
-      <x:c r="F140" s="13"/>
+      <x:c r="F140" s="16"/>
       <x:c r="G140" s="16"/>
       <x:c r="H140" s="16"/>
       <x:c r="I140" s="17"/>
@@ -4930,7 +4930,7 @@
       <x:c r="C141" s="13"/>
       <x:c r="D141" s="13"/>
       <x:c r="E141" s="13"/>
-      <x:c r="F141" s="13"/>
+      <x:c r="F141" s="16"/>
       <x:c r="G141" s="16"/>
       <x:c r="H141" s="16"/>
       <x:c r="I141" s="17"/>
@@ -4961,7 +4961,7 @@
       <x:c r="C142" s="13"/>
       <x:c r="D142" s="13"/>
       <x:c r="E142" s="13"/>
-      <x:c r="F142" s="13"/>
+      <x:c r="F142" s="16"/>
       <x:c r="G142" s="16"/>
       <x:c r="H142" s="16"/>
       <x:c r="I142" s="17"/>
@@ -4992,7 +4992,7 @@
       <x:c r="C143" s="13"/>
       <x:c r="D143" s="13"/>
       <x:c r="E143" s="13"/>
-      <x:c r="F143" s="13"/>
+      <x:c r="F143" s="16"/>
       <x:c r="G143" s="16"/>
       <x:c r="H143" s="16"/>
       <x:c r="I143" s="17"/>
@@ -5023,7 +5023,7 @@
       <x:c r="C144" s="13"/>
       <x:c r="D144" s="13"/>
       <x:c r="E144" s="13"/>
-      <x:c r="F144" s="13"/>
+      <x:c r="F144" s="16"/>
       <x:c r="G144" s="16"/>
       <x:c r="H144" s="16"/>
       <x:c r="I144" s="17"/>
@@ -5054,7 +5054,7 @@
       <x:c r="C145" s="13"/>
       <x:c r="D145" s="13"/>
       <x:c r="E145" s="13"/>
-      <x:c r="F145" s="13"/>
+      <x:c r="F145" s="16"/>
       <x:c r="G145" s="16"/>
       <x:c r="H145" s="16"/>
       <x:c r="I145" s="17"/>
@@ -5085,7 +5085,7 @@
       <x:c r="C146" s="13"/>
       <x:c r="D146" s="13"/>
       <x:c r="E146" s="13"/>
-      <x:c r="F146" s="13"/>
+      <x:c r="F146" s="16"/>
       <x:c r="G146" s="16"/>
       <x:c r="H146" s="16"/>
       <x:c r="I146" s="17"/>
@@ -5116,7 +5116,7 @@
       <x:c r="C147" s="13"/>
       <x:c r="D147" s="13"/>
       <x:c r="E147" s="13"/>
-      <x:c r="F147" s="13"/>
+      <x:c r="F147" s="16"/>
       <x:c r="G147" s="16"/>
       <x:c r="H147" s="16"/>
       <x:c r="I147" s="17"/>
@@ -5147,7 +5147,7 @@
       <x:c r="C148" s="13"/>
       <x:c r="D148" s="13"/>
       <x:c r="E148" s="13"/>
-      <x:c r="F148" s="13"/>
+      <x:c r="F148" s="16"/>
       <x:c r="G148" s="16"/>
       <x:c r="H148" s="16"/>
       <x:c r="I148" s="17"/>
@@ -5178,7 +5178,7 @@
       <x:c r="C149" s="13"/>
       <x:c r="D149" s="13"/>
       <x:c r="E149" s="13"/>
-      <x:c r="F149" s="13"/>
+      <x:c r="F149" s="16"/>
       <x:c r="G149" s="16"/>
       <x:c r="H149" s="16"/>
       <x:c r="I149" s="17"/>
@@ -5209,7 +5209,7 @@
       <x:c r="C150" s="13"/>
       <x:c r="D150" s="13"/>
       <x:c r="E150" s="13"/>
-      <x:c r="F150" s="13"/>
+      <x:c r="F150" s="16"/>
       <x:c r="G150" s="16"/>
       <x:c r="H150" s="16"/>
       <x:c r="I150" s="17"/>
@@ -5240,7 +5240,7 @@
       <x:c r="C151" s="13"/>
       <x:c r="D151" s="13"/>
       <x:c r="E151" s="13"/>
-      <x:c r="F151" s="13"/>
+      <x:c r="F151" s="16"/>
       <x:c r="G151" s="16"/>
       <x:c r="H151" s="16"/>
       <x:c r="I151" s="17"/>
@@ -5271,7 +5271,7 @@
       <x:c r="C152" s="13"/>
       <x:c r="D152" s="13"/>
       <x:c r="E152" s="13"/>
-      <x:c r="F152" s="13"/>
+      <x:c r="F152" s="16"/>
       <x:c r="G152" s="16"/>
       <x:c r="H152" s="16"/>
       <x:c r="I152" s="17"/>
@@ -5302,7 +5302,7 @@
       <x:c r="C153" s="13"/>
       <x:c r="D153" s="13"/>
       <x:c r="E153" s="13"/>
-      <x:c r="F153" s="13"/>
+      <x:c r="F153" s="16"/>
       <x:c r="G153" s="16"/>
       <x:c r="H153" s="16"/>
       <x:c r="I153" s="17"/>
@@ -5333,7 +5333,7 @@
       <x:c r="C154" s="13"/>
       <x:c r="D154" s="13"/>
       <x:c r="E154" s="13"/>
-      <x:c r="F154" s="13"/>
+      <x:c r="F154" s="16"/>
       <x:c r="G154" s="16"/>
       <x:c r="H154" s="16"/>
       <x:c r="I154" s="17"/>
@@ -5364,7 +5364,7 @@
       <x:c r="C155" s="13"/>
       <x:c r="D155" s="13"/>
       <x:c r="E155" s="13"/>
-      <x:c r="F155" s="13"/>
+      <x:c r="F155" s="16"/>
       <x:c r="G155" s="16"/>
       <x:c r="H155" s="16"/>
       <x:c r="I155" s="17"/>
@@ -5395,7 +5395,7 @@
       <x:c r="C156" s="13"/>
       <x:c r="D156" s="13"/>
       <x:c r="E156" s="13"/>
-      <x:c r="F156" s="13"/>
+      <x:c r="F156" s="16"/>
       <x:c r="G156" s="16"/>
       <x:c r="H156" s="16"/>
       <x:c r="I156" s="17"/>
@@ -5426,7 +5426,7 @@
       <x:c r="C157" s="13"/>
       <x:c r="D157" s="13"/>
       <x:c r="E157" s="13"/>
-      <x:c r="F157" s="13"/>
+      <x:c r="F157" s="16"/>
       <x:c r="G157" s="16"/>
       <x:c r="H157" s="16"/>
       <x:c r="I157" s="17"/>
@@ -5457,7 +5457,7 @@
       <x:c r="C158" s="13"/>
       <x:c r="D158" s="13"/>
       <x:c r="E158" s="13"/>
-      <x:c r="F158" s="13"/>
+      <x:c r="F158" s="16"/>
       <x:c r="G158" s="16"/>
       <x:c r="H158" s="16"/>
       <x:c r="I158" s="17"/>
@@ -5488,7 +5488,7 @@
       <x:c r="C159" s="13"/>
       <x:c r="D159" s="13"/>
       <x:c r="E159" s="13"/>
-      <x:c r="F159" s="13"/>
+      <x:c r="F159" s="16"/>
       <x:c r="G159" s="16"/>
       <x:c r="H159" s="16"/>
       <x:c r="I159" s="17"/>
@@ -5519,7 +5519,7 @@
       <x:c r="C160" s="13"/>
       <x:c r="D160" s="13"/>
       <x:c r="E160" s="13"/>
-      <x:c r="F160" s="13"/>
+      <x:c r="F160" s="16"/>
       <x:c r="G160" s="16"/>
       <x:c r="H160" s="16"/>
       <x:c r="I160" s="17"/>
@@ -5550,7 +5550,7 @@
       <x:c r="C161" s="13"/>
       <x:c r="D161" s="13"/>
       <x:c r="E161" s="13"/>
-      <x:c r="F161" s="13"/>
+      <x:c r="F161" s="16"/>
       <x:c r="G161" s="16"/>
       <x:c r="H161" s="16"/>
       <x:c r="I161" s="17"/>
@@ -5581,7 +5581,7 @@
       <x:c r="C162" s="13"/>
       <x:c r="D162" s="13"/>
       <x:c r="E162" s="13"/>
-      <x:c r="F162" s="13"/>
+      <x:c r="F162" s="16"/>
       <x:c r="G162" s="16"/>
       <x:c r="H162" s="16"/>
       <x:c r="I162" s="17"/>
@@ -5612,7 +5612,7 @@
       <x:c r="C163" s="13"/>
       <x:c r="D163" s="13"/>
       <x:c r="E163" s="13"/>
-      <x:c r="F163" s="13"/>
+      <x:c r="F163" s="16"/>
       <x:c r="G163" s="16"/>
       <x:c r="H163" s="16"/>
       <x:c r="I163" s="17"/>
@@ -5643,7 +5643,7 @@
       <x:c r="C164" s="13"/>
       <x:c r="D164" s="13"/>
       <x:c r="E164" s="13"/>
-      <x:c r="F164" s="13"/>
+      <x:c r="F164" s="16"/>
       <x:c r="G164" s="16"/>
       <x:c r="H164" s="16"/>
       <x:c r="I164" s="17"/>
@@ -5674,7 +5674,7 @@
       <x:c r="C165" s="13"/>
       <x:c r="D165" s="13"/>
       <x:c r="E165" s="13"/>
-      <x:c r="F165" s="13"/>
+      <x:c r="F165" s="16"/>
       <x:c r="G165" s="16"/>
       <x:c r="H165" s="16"/>
       <x:c r="I165" s="17"/>
@@ -5705,7 +5705,7 @@
       <x:c r="C166" s="13"/>
       <x:c r="D166" s="13"/>
       <x:c r="E166" s="13"/>
-      <x:c r="F166" s="13"/>
+      <x:c r="F166" s="16"/>
       <x:c r="G166" s="16"/>
       <x:c r="H166" s="16"/>
       <x:c r="I166" s="17"/>
@@ -5736,7 +5736,7 @@
       <x:c r="C167" s="13"/>
       <x:c r="D167" s="13"/>
       <x:c r="E167" s="13"/>
-      <x:c r="F167" s="13"/>
+      <x:c r="F167" s="16"/>
       <x:c r="G167" s="16"/>
       <x:c r="H167" s="16"/>
       <x:c r="I167" s="17"/>
@@ -5767,7 +5767,7 @@
       <x:c r="C168" s="13"/>
       <x:c r="D168" s="13"/>
       <x:c r="E168" s="13"/>
-      <x:c r="F168" s="13"/>
+      <x:c r="F168" s="16"/>
       <x:c r="G168" s="16"/>
       <x:c r="H168" s="16"/>
       <x:c r="I168" s="17"/>
@@ -5798,7 +5798,7 @@
       <x:c r="C169" s="13"/>
       <x:c r="D169" s="13"/>
       <x:c r="E169" s="13"/>
-      <x:c r="F169" s="13"/>
+      <x:c r="F169" s="16"/>
       <x:c r="G169" s="16"/>
       <x:c r="H169" s="16"/>
       <x:c r="I169" s="17"/>
@@ -5829,7 +5829,7 @@
       <x:c r="C170" s="13"/>
       <x:c r="D170" s="13"/>
       <x:c r="E170" s="13"/>
-      <x:c r="F170" s="13"/>
+      <x:c r="F170" s="16"/>
       <x:c r="G170" s="16"/>
       <x:c r="H170" s="16"/>
       <x:c r="I170" s="17"/>
@@ -5860,7 +5860,7 @@
       <x:c r="C171" s="13"/>
       <x:c r="D171" s="13"/>
       <x:c r="E171" s="13"/>
-      <x:c r="F171" s="13"/>
+      <x:c r="F171" s="16"/>
       <x:c r="G171" s="16"/>
       <x:c r="H171" s="16"/>
       <x:c r="I171" s="17"/>
@@ -5891,7 +5891,7 @@
       <x:c r="C172" s="13"/>
       <x:c r="D172" s="13"/>
       <x:c r="E172" s="13"/>
-      <x:c r="F172" s="13"/>
+      <x:c r="F172" s="16"/>
       <x:c r="G172" s="16"/>
       <x:c r="H172" s="16"/>
       <x:c r="I172" s="17"/>
@@ -5922,7 +5922,7 @@
       <x:c r="C173" s="13"/>
       <x:c r="D173" s="13"/>
       <x:c r="E173" s="13"/>
-      <x:c r="F173" s="13"/>
+      <x:c r="F173" s="16"/>
       <x:c r="G173" s="16"/>
       <x:c r="H173" s="16"/>
       <x:c r="I173" s="17"/>
@@ -5953,7 +5953,7 @@
       <x:c r="C174" s="13"/>
       <x:c r="D174" s="13"/>
       <x:c r="E174" s="13"/>
-      <x:c r="F174" s="13"/>
+      <x:c r="F174" s="16"/>
       <x:c r="G174" s="16"/>
       <x:c r="H174" s="16"/>
       <x:c r="I174" s="17"/>
@@ -5984,7 +5984,7 @@
       <x:c r="C175" s="13"/>
       <x:c r="D175" s="13"/>
       <x:c r="E175" s="13"/>
-      <x:c r="F175" s="13"/>
+      <x:c r="F175" s="16"/>
       <x:c r="G175" s="16"/>
       <x:c r="H175" s="16"/>
       <x:c r="I175" s="17"/>
@@ -6015,7 +6015,7 @@
       <x:c r="C176" s="13"/>
       <x:c r="D176" s="13"/>
       <x:c r="E176" s="13"/>
-      <x:c r="F176" s="13"/>
+      <x:c r="F176" s="16"/>
       <x:c r="G176" s="16"/>
       <x:c r="H176" s="16"/>
       <x:c r="I176" s="17"/>
@@ -6046,7 +6046,7 @@
       <x:c r="C177" s="13"/>
       <x:c r="D177" s="13"/>
       <x:c r="E177" s="13"/>
-      <x:c r="F177" s="13"/>
+      <x:c r="F177" s="16"/>
       <x:c r="G177" s="16"/>
       <x:c r="H177" s="16"/>
       <x:c r="I177" s="17"/>
@@ -6077,7 +6077,7 @@
       <x:c r="C178" s="13"/>
       <x:c r="D178" s="13"/>
       <x:c r="E178" s="13"/>
-      <x:c r="F178" s="13"/>
+      <x:c r="F178" s="16"/>
       <x:c r="G178" s="16"/>
       <x:c r="H178" s="16"/>
       <x:c r="I178" s="17"/>
@@ -6108,7 +6108,7 @@
       <x:c r="C179" s="13"/>
       <x:c r="D179" s="13"/>
       <x:c r="E179" s="13"/>
-      <x:c r="F179" s="13"/>
+      <x:c r="F179" s="16"/>
       <x:c r="G179" s="16"/>
       <x:c r="H179" s="16"/>
       <x:c r="I179" s="17"/>
@@ -6139,7 +6139,7 @@
       <x:c r="C180" s="13"/>
       <x:c r="D180" s="13"/>
       <x:c r="E180" s="13"/>
-      <x:c r="F180" s="13"/>
+      <x:c r="F180" s="16"/>
       <x:c r="G180" s="16"/>
       <x:c r="H180" s="16"/>
       <x:c r="I180" s="17"/>
@@ -6170,7 +6170,7 @@
       <x:c r="C181" s="13"/>
       <x:c r="D181" s="13"/>
       <x:c r="E181" s="13"/>
-      <x:c r="F181" s="13"/>
+      <x:c r="F181" s="16"/>
       <x:c r="G181" s="16"/>
       <x:c r="H181" s="16"/>
       <x:c r="I181" s="17"/>
@@ -6201,7 +6201,7 @@
       <x:c r="C182" s="13"/>
       <x:c r="D182" s="13"/>
       <x:c r="E182" s="13"/>
-      <x:c r="F182" s="13"/>
+      <x:c r="F182" s="16"/>
       <x:c r="G182" s="16"/>
       <x:c r="H182" s="16"/>
       <x:c r="I182" s="17"/>
@@ -6232,7 +6232,7 @@
       <x:c r="C183" s="13"/>
       <x:c r="D183" s="13"/>
       <x:c r="E183" s="13"/>
-      <x:c r="F183" s="13"/>
+      <x:c r="F183" s="16"/>
       <x:c r="G183" s="16"/>
       <x:c r="H183" s="16"/>
       <x:c r="I183" s="17"/>
@@ -6263,7 +6263,7 @@
       <x:c r="C184" s="13"/>
       <x:c r="D184" s="13"/>
       <x:c r="E184" s="13"/>
-      <x:c r="F184" s="13"/>
+      <x:c r="F184" s="16"/>
       <x:c r="G184" s="16"/>
       <x:c r="H184" s="16"/>
       <x:c r="I184" s="17"/>
@@ -6294,7 +6294,7 @@
       <x:c r="C185" s="13"/>
       <x:c r="D185" s="13"/>
       <x:c r="E185" s="13"/>
-      <x:c r="F185" s="13"/>
+      <x:c r="F185" s="16"/>
       <x:c r="G185" s="16"/>
       <x:c r="H185" s="16"/>
       <x:c r="I185" s="17"/>
@@ -6325,7 +6325,7 @@
       <x:c r="C186" s="13"/>
       <x:c r="D186" s="13"/>
       <x:c r="E186" s="13"/>
-      <x:c r="F186" s="13"/>
+      <x:c r="F186" s="16"/>
       <x:c r="G186" s="16"/>
       <x:c r="H186" s="16"/>
       <x:c r="I186" s="17"/>
@@ -6356,7 +6356,7 @@
       <x:c r="C187" s="13"/>
       <x:c r="D187" s="13"/>
       <x:c r="E187" s="13"/>
-      <x:c r="F187" s="13"/>
+      <x:c r="F187" s="16"/>
       <x:c r="G187" s="16"/>
       <x:c r="H187" s="16"/>
       <x:c r="I187" s="17"/>
@@ -6387,7 +6387,7 @@
       <x:c r="C188" s="13"/>
       <x:c r="D188" s="13"/>
       <x:c r="E188" s="13"/>
-      <x:c r="F188" s="13"/>
+      <x:c r="F188" s="16"/>
       <x:c r="G188" s="16"/>
       <x:c r="H188" s="16"/>
       <x:c r="I188" s="17"/>
@@ -6418,7 +6418,7 @@
       <x:c r="C189" s="13"/>
       <x:c r="D189" s="13"/>
       <x:c r="E189" s="13"/>
-      <x:c r="F189" s="13"/>
+      <x:c r="F189" s="16"/>
       <x:c r="G189" s="16"/>
       <x:c r="H189" s="16"/>
       <x:c r="I189" s="17"/>
@@ -6449,7 +6449,7 @@
       <x:c r="C190" s="13"/>
       <x:c r="D190" s="13"/>
       <x:c r="E190" s="13"/>
-      <x:c r="F190" s="13"/>
+      <x:c r="F190" s="16"/>
       <x:c r="G190" s="16"/>
       <x:c r="H190" s="16"/>
       <x:c r="I190" s="17"/>
@@ -6480,7 +6480,7 @@
       <x:c r="C191" s="13"/>
       <x:c r="D191" s="13"/>
       <x:c r="E191" s="13"/>
-      <x:c r="F191" s="13"/>
+      <x:c r="F191" s="16"/>
       <x:c r="G191" s="16"/>
       <x:c r="H191" s="16"/>
       <x:c r="I191" s="17"/>
@@ -6511,7 +6511,7 @@
       <x:c r="C192" s="13"/>
       <x:c r="D192" s="13"/>
       <x:c r="E192" s="13"/>
-      <x:c r="F192" s="13"/>
+      <x:c r="F192" s="16"/>
       <x:c r="G192" s="16"/>
       <x:c r="H192" s="16"/>
       <x:c r="I192" s="17"/>
@@ -6542,7 +6542,7 @@
       <x:c r="C193" s="13"/>
       <x:c r="D193" s="13"/>
       <x:c r="E193" s="13"/>
-      <x:c r="F193" s="13"/>
+      <x:c r="F193" s="16"/>
       <x:c r="G193" s="16"/>
       <x:c r="H193" s="16"/>
       <x:c r="I193" s="17"/>
@@ -6573,7 +6573,7 @@
       <x:c r="C194" s="13"/>
       <x:c r="D194" s="13"/>
       <x:c r="E194" s="13"/>
-      <x:c r="F194" s="13"/>
+      <x:c r="F194" s="16"/>
       <x:c r="G194" s="16"/>
       <x:c r="H194" s="16"/>
       <x:c r="I194" s="17"/>
@@ -6604,7 +6604,7 @@
       <x:c r="C195" s="13"/>
       <x:c r="D195" s="13"/>
       <x:c r="E195" s="13"/>
-      <x:c r="F195" s="13"/>
+      <x:c r="F195" s="16"/>
       <x:c r="G195" s="16"/>
       <x:c r="H195" s="16"/>
       <x:c r="I195" s="17"/>
@@ -6635,7 +6635,7 @@
       <x:c r="C196" s="13"/>
       <x:c r="D196" s="13"/>
       <x:c r="E196" s="13"/>
-      <x:c r="F196" s="13"/>
+      <x:c r="F196" s="16"/>
       <x:c r="G196" s="16"/>
       <x:c r="H196" s="16"/>
       <x:c r="I196" s="17"/>
@@ -6666,7 +6666,7 @@
       <x:c r="C197" s="13"/>
       <x:c r="D197" s="13"/>
       <x:c r="E197" s="13"/>
-      <x:c r="F197" s="13"/>
+      <x:c r="F197" s="16"/>
       <x:c r="G197" s="16"/>
       <x:c r="H197" s="16"/>
       <x:c r="I197" s="17"/>
@@ -6697,7 +6697,7 @@
       <x:c r="C198" s="13"/>
       <x:c r="D198" s="13"/>
       <x:c r="E198" s="13"/>
-      <x:c r="F198" s="13"/>
+      <x:c r="F198" s="16"/>
       <x:c r="G198" s="16"/>
       <x:c r="H198" s="16"/>
       <x:c r="I198" s="17"/>
@@ -6728,7 +6728,7 @@
       <x:c r="C199" s="13"/>
       <x:c r="D199" s="13"/>
       <x:c r="E199" s="13"/>
-      <x:c r="F199" s="13"/>
+      <x:c r="F199" s="16"/>
       <x:c r="G199" s="16"/>
       <x:c r="H199" s="16"/>
       <x:c r="I199" s="17"/>
@@ -6759,7 +6759,7 @@
       <x:c r="C200" s="13"/>
       <x:c r="D200" s="13"/>
       <x:c r="E200" s="13"/>
-      <x:c r="F200" s="13"/>
+      <x:c r="F200" s="16"/>
       <x:c r="G200" s="16"/>
       <x:c r="H200" s="16"/>
       <x:c r="I200" s="17"/>
@@ -6790,7 +6790,7 @@
       <x:c r="C201" s="13"/>
       <x:c r="D201" s="13"/>
       <x:c r="E201" s="13"/>
-      <x:c r="F201" s="13"/>
+      <x:c r="F201" s="16"/>
       <x:c r="G201" s="16"/>
       <x:c r="H201" s="16"/>
       <x:c r="I201" s="17"/>
@@ -6944,11 +6944,11 @@
       <x:c r="B7" s="3" t="str">
         <x:v>ferruleSku</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="str">
-        <x:v>必填</x:v>
+      <x:c r="C7" s="20" t="str">
+        <x:v>选填</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str">
-        <x:v>Update 新增时必填。PartialUpdate 空白保留原值；Delete 仅需操作和兼容编号。不可通过更新更换三件套 SKU。</x:v>
+        <x:v>选填。PartialUpdate 空白保留原值；Delete 仅需操作和兼容编号。不可通过更新更换三件套 SKU。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
